--- a/knowledge-source/术语库.xlsx
+++ b/knowledge-source/术语库.xlsx
@@ -43023,27 +43023,27 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Basic settings</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Конфигурация</t>
+          <t>Основные настройки</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>Configurações</t>
+          <t>Configurações básicas</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Configuración</t>
+          <t>Configuración básica</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>Cấu hình cơ bản</t>
+          <t>Cài đặt cơ bản</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
@@ -43078,7 +43078,7 @@
         </is>
       </c>
       <c r="Q545" s="2">
-        <v>46135.85928240741</v>
+        <v>46267.71665509259</v>
       </c>
     </row>
     <row r="546" ht="25.5" customHeight="1">
